--- a/lcr_analyses/clustering/carriers/SEG/cluster_summaries_pam.xlsx
+++ b/lcr_analyses/clustering/carriers/SEG/cluster_summaries_pam.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4432,4 +4436,5598 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.04069767441860465</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02985074626865672</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.07462686567164178</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8507462686567164</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.04477611940298507</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.04477611940298507</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.04477611940298507</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.02985074626865672</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9104477611940298</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.02985074626865672</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.3725490196078431</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8846153846153846</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.196969696969697</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>45</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.03139013452914798</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07462686567164178</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1641791044776119</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5522388059701493</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02985074626865672</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.02985074626865672</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.04477611940298507</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9850746268656716</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.02985074626865672</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.7627118644067796</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.6538461538461539</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.06451612903225808</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1100917431192661</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3414634146341464</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6229508196721312</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9122807017543859</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0333357999112032</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1346153846153846</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1923076923076923</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0576923076923077</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8633540372670807</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.06066176470588235</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02796420581655481</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.04098360655737705</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8524590163934426</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>32</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0518952158760333</v>
+      </c>
+      <c r="E7" t="n">
+        <v>21</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3484848484848485</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.7362637362637363</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.09413067552602436</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.08738738738738738</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.05238095238095238</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.008333333333333333</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>36</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1160248121104878</v>
+      </c>
+      <c r="E8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.9350210970464135</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.1285085305448541</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.02325581395348837</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.03015873015873016</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.9205263157894736</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.4431524547803617</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.0209450069485805</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4536878216123499</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.3741631162507608</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.4354166666666667</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>31</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02665006226650062</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.1775210084033614</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.007692307692307695</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8973684210526316</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.02272727272727273</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.6210359408033828</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.03176312019463071</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07575757575757576</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1060606060606061</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1060606060606061</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1207729468599033</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.04880952380952381</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8038461538461539</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.7629348795718109</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.6550480769230769</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.0608294930875576</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1043986223686945</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1923076923076923</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3596205962059621</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6191677175283733</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.03722677595628415</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9126620900076277</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2943722943722943</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.3100517368810052</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.5203632361034672</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>48</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.03546461393449062</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1041666666666667</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1213235294117647</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.05718954248366013</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8633540372670807</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.04235187211066803</v>
+      </c>
+      <c r="E6" t="n">
+        <v>22.19642857142857</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01724137931034483</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.01724137931034483</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9655172413793104</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01724137931034483</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.01724137931034483</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.3129370629370629</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.2936507936507936</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.06042351223074115</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.002525252525252525</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.00684931506849315</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.04446640316205534</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1819852941176471</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>29</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.08119079837618404</v>
+      </c>
+      <c r="E7" t="n">
+        <v>21</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5517241379310345</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3448275862068966</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3286713286713286</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.7362637362637363</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.09302325581395349</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1081081081081081</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1160248121104878</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25.83333333333334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08823529411764706</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.2058823529411765</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.9350210970464135</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.1206060606060606</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.02478580171358629</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.9205263157894736</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.459830866807611</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.01438923395445135</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4775193798449612</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.3921188630490956</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.428030303030303</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02796420581655481</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.04098360655737705</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.8524590163934426</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02602739726027397</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.01538461538461539</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.6511627906976745</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>42</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.02917986980203506</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20.825</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02380952380952381</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.119047619047619</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.02380952380952381</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8759590792838874</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.04356060606060606</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8186090225563909</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.01741031052155562</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.6117255449371846</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.6923386663803286</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.5311124234940405</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1441647597254004</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1043986223686945</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1923076923076923</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3596205962059621</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6191677175283733</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.03722677595628415</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9126620900076277</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2943722943722943</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.3100517368810052</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.5203632361034672</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>48</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.03546461393449062</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1041666666666667</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1213235294117647</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.05718954248366013</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8633540372670807</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.04069767441860465</v>
+      </c>
+      <c r="E6" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1228070175438596</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9122807017543859</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1228070175438596</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9649122807017544</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.3015873015873016</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.04347826086956523</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>37</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.08277466105100942</v>
+      </c>
+      <c r="E7" t="n">
+        <v>21</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3286713286713286</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.7385022385022385</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.09302325581395349</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.108999108999109</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.7470930232558139</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1160248121104878</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25.83333333333334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08823529411764706</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.2058823529411765</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.9350210970464135</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.1206060606060606</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.02478580171358629</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.9205263157894736</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.459830866807611</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.01438923395445135</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4775193798449612</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.3921188630490956</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.428030303030303</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02796420581655481</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.04098360655737705</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.8524590163934426</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>27</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.032560706401766</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2592592592592592</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.8260869565217391</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.04069767441860465</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1228070175438596</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9122807017543859</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1228070175438596</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9649122807017544</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.3015873015873016</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.04347826086956523</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>37</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>42</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.02917986980203506</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20.825</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02380952380952381</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.119047619047619</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.02380952380952381</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8759590792838874</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.04356060606060606</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8186090225563909</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.01741031052155562</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.6117255449371846</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.6923386663803286</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.5311124234940405</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1441647597254004</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1102941176470588</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3414634146341464</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6229508196721312</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9122807017543859</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>47</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0425531914893617</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3829787234042553</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1063829787234043</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2127659574468085</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0425531914893617</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9148936170212766</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.3142857142857143</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.7252747252747253</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0430622009569378</v>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1160248121104878</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25.83333333333334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08823529411764706</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.2058823529411765</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.9350210970464135</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.1206060606060606</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.02478580171358629</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.9205263157894736</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.459830866807611</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.01438923395445135</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4775193798449612</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.3921188630490956</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.428030303030303</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02796420581655481</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.02941176470588235</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.04098360655737705</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.8524590163934426</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>27</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.032560706401766</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2592592592592592</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.8260869565217391</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.02602739726027397</v>
+      </c>
+      <c r="E11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.1449275362318841</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.6511627906976745</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>